--- a/assessment_forms/021_development_knowledge_assessment--assessment_forms.xlsx
+++ b/assessment_forms/021_development_knowledge_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Welcome to the Development Knowledge Assessment. Please answer the questions to the best of your knowledge.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -551,7 +555,11 @@
           <t>What is the primary goal of a code review?</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Choose the best answer.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -574,7 +582,11 @@
           <t>question1_answer</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please enter your answer.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -594,10 +606,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is the purpose of a code review?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is the main focus of a code review?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question2_answer</t>
+          <t>question3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>question2_answer</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is the primary function of a software architect?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Choose the best answer.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question3</t>
+          <t>question4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is the first step in the SDLC process?</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What is the main objective of a code review?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question4</t>
+          <t>question5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is the primary goal of a code review?</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is the main purpose of a code review?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please enter your answer.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question5</t>
+          <t>question6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is the purpose of a code review?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What is the main objective of code reviews?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please enter your answer.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question5_answer</t>
+          <t>question7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>question5_answer</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is the main purpose of code reviews?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question6</t>
+          <t>question8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is the first step in the SDLC process?</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Question8</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Choose the best answer.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question6_answer</t>
+          <t>question9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>question6_answer</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Question9</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please enter your answer.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,20 +812,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question7</t>
+          <t>question10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is the primary function of a software architect?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What is the main objective of code review?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please enter your answer.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -796,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question7_answer</t>
+          <t>question11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>question7_answer</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>What is the main focus of code reviews?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please enter your answer.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -819,15 +871,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question8</t>
+          <t>question12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What is the main focus of a code review?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Question12</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -842,15 +898,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question8_answer</t>
+          <t>question13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>question8_answer</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Question13</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please enter your answer.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -860,20 +920,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question9</t>
+          <t>question14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What is the main goal of code review?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Question14</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please enter your answer.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -888,15 +952,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>question9_answer</t>
+          <t>question15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>question9_answer</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Question15</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please enter your answer.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -906,182 +974,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>question10</t>
+          <t>question16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What is the main focus of code review?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Question16</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please enter your answer.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question10_answer</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>question10_answer</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question11</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What is the main objective of code review?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question11_answer</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>question11_answer</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question12</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is the main purpose of code review?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question12_answer</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>question12_answer</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question13</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What is the main objective of code reviews?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question13_answer</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>question13_answer</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +1009,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1042,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'improve_code_quality'}</t>
+          <t>improve_code_quality</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Improve code quality'}</t>
+          <t>Improve code quality</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1059,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'identify_security_issues'}</t>
+          <t>identify_security_issues</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Identify security issues'}</t>
+          <t>Identify security issues</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1076,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'document_code_changes'}</t>
+          <t>document_code_changes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Document code changes'}</t>
+          <t>Document code changes</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1093,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1110,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'improve_code_quality'}</t>
+          <t>improve_code_quality</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Improve code quality'}</t>
+          <t>Improve code quality</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1127,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'identify_security_issues'}</t>
+          <t>identify_security_issues</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Identify security issues'}</t>
+          <t>Identify security issues</t>
         </is>
       </c>
     </row>
@@ -1233,29 +1144,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'document_code_changes'}</t>
+          <t>document_code_changes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Document code changes'}</t>
+          <t>Document code changes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question2_choices</t>
+          <t>question3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other_(please_specify)'}</t>
+          <t>designs_overall_system_architecture</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other (please specify)'}</t>
+          <t>Designs overall system architecture</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1178,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'planning'}</t>
+          <t>leads_development_team</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Planning'}</t>
+          <t>Leads development team</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1195,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'design'}</t>
+          <t>documents_code_changes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Design'}</t>
+          <t>Documents code changes</t>
         </is>
       </c>
     </row>
@@ -1301,46 +1212,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'development'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Development'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question3_choices</t>
+          <t>question4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'testing'}</t>
+          <t>improve_code_quality</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Testing'}</t>
+          <t>Improve code quality</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question3_choices</t>
+          <t>question4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'deployment'}</t>
+          <t>identify_security_issues</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Deployment'}</t>
+          <t>Identify security issues</t>
         </is>
       </c>
     </row>
@@ -1352,556 +1263,182 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'improve_code_quality'}</t>
+          <t>document_code_changes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Improve code quality'}</t>
+          <t>Document code changes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question4_choices</t>
+          <t>question7_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'identify_security_issues'}</t>
+          <t>improve_code_quality</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Identify security issues'}</t>
+          <t>Improve code quality</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question4_choices</t>
+          <t>question7_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'document_code_changes'}</t>
+          <t>identify_security_issues</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Document code changes'}</t>
+          <t>Identify security issues</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question5_choices</t>
+          <t>question7_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'improve_code_quality'}</t>
+          <t>document_code_changes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Improve code quality'}</t>
+          <t>Document code changes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question5_choices</t>
+          <t>question8_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'identify_security_issues'}</t>
+          <t>designs_overall_system_architecture</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Identify security issues'}</t>
+          <t>Designs overall system architecture</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question5_choices</t>
+          <t>question8_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'document_code_changes'}</t>
+          <t>leads_development_team</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Document code changes'}</t>
+          <t>Leads development team</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question6_choices</t>
+          <t>question8_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'planning'}</t>
+          <t>documents_code_changes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Planning'}</t>
+          <t>Documents code changes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question6_choices</t>
+          <t>question8_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'design'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Design'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question6_choices</t>
+          <t>question12_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'development'}</t>
+          <t>improve_code_quality</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Development'}</t>
+          <t>Improve code quality</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>question6_choices</t>
+          <t>question12_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'testing'}</t>
+          <t>identify_security_issues</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Testing'}</t>
+          <t>Identify security issues</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>question6_choices</t>
+          <t>question12_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'deployment'}</t>
+          <t>document_code_changes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Deployment'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>question7_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'designs_overall_system_architecture'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Designs overall system architecture'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>question7_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'leads_development_team'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Leads development team'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>question7_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'documents_code_changes'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Documents code changes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>question7_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'label':_'other_(please_specify)'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'label': 'Other (please specify)'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>question8_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'improve_code_quality'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Improve code quality'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>question8_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'identify_security_issues'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Identify security issues'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>question8_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'document_code_changes'}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Document code changes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>question9_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'improve_code_quality'}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Improve code quality'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>question9_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'identify_security_issues'}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Identify security issues'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>question9_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'document_code_changes'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Document code changes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>question10_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'improve_code_quality'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Improve code quality'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>question10_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'identify_security_issues'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Identify security issues'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>question10_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'document_code_changes'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Document code changes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>question11_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'improve_code_quality'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Improve code quality'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>question11_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'identify_security_issues'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Identify security issues'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>question11_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'document_code_changes'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Document code changes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>question12_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'improve_code_quality'}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Improve code quality'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>question12_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'identify_security_issues'}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Identify security issues'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>question12_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'document_code_changes'}</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Document code changes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>question13_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'improve_code_quality'}</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Improve code quality'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>question13_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'identify_security_issues'}</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Identify security issues'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>question13_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'document_code_changes'}</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Document code changes'}</t>
+          <t>Document code changes</t>
         </is>
       </c>
     </row>
